--- a/research/traditional_assets/database/data/malaysia/malaysia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0718</v>
+        <v>-0.00233</v>
       </c>
       <c r="E2">
-        <v>0.29</v>
+        <v>-0.0211</v>
       </c>
       <c r="G2">
-        <v>0.06043428571428572</v>
+        <v>0.06556245686680469</v>
       </c>
       <c r="H2">
-        <v>0.06043428571428572</v>
+        <v>0.06556245686680469</v>
       </c>
       <c r="I2">
-        <v>0.08882285714285715</v>
+        <v>-0.01573498964803312</v>
       </c>
       <c r="J2">
-        <v>0.05123885714285714</v>
+        <v>-0.01401961782574755</v>
       </c>
       <c r="K2">
-        <v>23.33</v>
+        <v>-17.43</v>
       </c>
       <c r="L2">
-        <v>0.05332571428571429</v>
+        <v>-0.06014492753623188</v>
       </c>
       <c r="M2">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>0.007731305449936628</v>
+        <v>0.00900163666121113</v>
       </c>
       <c r="O2">
-        <v>0.05229318474067723</v>
+        <v>-0.06310958118187035</v>
       </c>
       <c r="P2">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Q2">
-        <v>0.007731305449936628</v>
+        <v>0.00900163666121113</v>
       </c>
       <c r="R2">
-        <v>0.05229318474067723</v>
+        <v>-0.06310958118187035</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>70.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="V2">
-        <v>0.4467680608365019</v>
+        <v>0.5654664484451718</v>
       </c>
       <c r="W2">
-        <v>0.05784697081475067</v>
+        <v>-0.08399967076154106</v>
       </c>
       <c r="X2">
-        <v>0.06866100555457075</v>
+        <v>0.1170504694703369</v>
       </c>
       <c r="Y2">
-        <v>-0.01081403473982008</v>
+        <v>-0.2010501402318779</v>
       </c>
       <c r="Z2">
-        <v>1.744723954760803</v>
+        <v>1.037200346449253</v>
       </c>
       <c r="AA2">
-        <v>0.08142769240683968</v>
+        <v>-0.03855900416597328</v>
       </c>
       <c r="AB2">
-        <v>0.06673211946142638</v>
+        <v>0.1015623355909855</v>
       </c>
       <c r="AC2">
-        <v>0.01469557294541331</v>
+        <v>-0.1401213397569588</v>
       </c>
       <c r="AD2">
-        <v>4.126</v>
+        <v>13.696</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.126</v>
+        <v>13.696</v>
       </c>
       <c r="AG2">
-        <v>-66.374</v>
+        <v>-55.404</v>
       </c>
       <c r="AH2">
-        <v>0.02548077516890431</v>
+        <v>0.1007829516689233</v>
       </c>
       <c r="AI2">
-        <v>0.01162168404567553</v>
+        <v>0.04655399801492882</v>
       </c>
       <c r="AJ2">
-        <v>-0.7259860433574693</v>
+        <v>-0.8294508653212765</v>
       </c>
       <c r="AK2">
-        <v>-0.2332792082270162</v>
+        <v>-0.2461349824075061</v>
       </c>
       <c r="AL2">
-        <v>0.258</v>
+        <v>0.966</v>
       </c>
       <c r="AM2">
-        <v>0.258</v>
+        <v>0.966</v>
       </c>
       <c r="AN2">
-        <v>0.09814462416745956</v>
+        <v>-6.253881278538815</v>
       </c>
       <c r="AO2">
-        <v>150.6201550387597</v>
+        <v>-4.720496894409938</v>
       </c>
       <c r="AP2">
-        <v>-1.57882968601332</v>
+        <v>25.2986301369863</v>
       </c>
       <c r="AQ2">
-        <v>150.6201550387597</v>
+        <v>-4.720496894409938</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0718</v>
+        <v>-0.00233</v>
       </c>
       <c r="E3">
-        <v>0.29</v>
+        <v>-0.0211</v>
       </c>
       <c r="G3">
-        <v>0.05110602593440122</v>
+        <v>0.119983948635634</v>
       </c>
       <c r="H3">
-        <v>0.05110602593440122</v>
+        <v>0.119983948635634</v>
       </c>
       <c r="I3">
-        <v>0.08517670989066869</v>
+        <v>0.02825040128410915</v>
       </c>
       <c r="J3">
-        <v>0.05568268497330282</v>
+        <v>0.0220908875615083</v>
       </c>
       <c r="K3">
-        <v>21.8</v>
+        <v>9.57</v>
       </c>
       <c r="L3">
-        <v>0.05542842613780829</v>
+        <v>0.03840288924558588</v>
       </c>
       <c r="M3">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>0.01044520547945206</v>
+        <v>0.01108870967741936</v>
       </c>
       <c r="O3">
-        <v>0.05596330275229357</v>
+        <v>0.1149425287356322</v>
       </c>
       <c r="P3">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Q3">
-        <v>0.01044520547945206</v>
+        <v>0.01108870967741936</v>
       </c>
       <c r="R3">
-        <v>0.05596330275229357</v>
+        <v>0.1149425287356322</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>52.1</v>
+        <v>60.5</v>
       </c>
       <c r="V3">
-        <v>0.4460616438356165</v>
+        <v>0.6098790322580645</v>
       </c>
       <c r="W3">
-        <v>0.1031220435193945</v>
+        <v>0.04260908281389136</v>
       </c>
       <c r="X3">
-        <v>0.06696558346423936</v>
+        <v>0.1030681526734813</v>
       </c>
       <c r="Y3">
-        <v>0.03615646005515515</v>
+        <v>-0.06045906985958989</v>
       </c>
       <c r="Z3">
-        <v>2.345175485671353</v>
+        <v>1.440995512790859</v>
       </c>
       <c r="AA3">
-        <v>0.1305856677757504</v>
+        <v>0.03183286984970086</v>
       </c>
       <c r="AB3">
-        <v>0.06681138095100191</v>
+        <v>0.1028456036327882</v>
       </c>
       <c r="AC3">
-        <v>0.06377428682474849</v>
+        <v>-0.07101273378308735</v>
       </c>
       <c r="AD3">
-        <v>0.436</v>
+        <v>0.396</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.436</v>
+        <v>0.396</v>
       </c>
       <c r="AG3">
-        <v>-51.664</v>
+        <v>-60.104</v>
       </c>
       <c r="AH3">
-        <v>0.003718994165614658</v>
+        <v>0.003976063295714687</v>
       </c>
       <c r="AI3">
-        <v>0.001937467782932509</v>
+        <v>0.001946940942791402</v>
       </c>
       <c r="AJ3">
-        <v>-0.7931712110046673</v>
+        <v>-1.537343973808062</v>
       </c>
       <c r="AK3">
-        <v>-0.298746357033816</v>
+        <v>-0.420613593102676</v>
       </c>
       <c r="AL3">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AN3">
-        <v>0.01221288515406162</v>
+        <v>0.04708680142687277</v>
       </c>
       <c r="AO3">
-        <v>8375</v>
+        <v>2346.666666666667</v>
       </c>
       <c r="AP3">
-        <v>-1.447170868347339</v>
+        <v>-7.146730083234245</v>
       </c>
       <c r="AQ3">
-        <v>8375</v>
+        <v>2346.666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.1434389140271493</v>
+        <v>-0.2684729064039409</v>
       </c>
       <c r="H4">
-        <v>0.1434389140271493</v>
+        <v>-0.2684729064039409</v>
       </c>
       <c r="I4">
-        <v>0.1212669683257919</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="J4">
-        <v>0.06063348416289593</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="K4">
-        <v>1.53</v>
+        <v>-27</v>
       </c>
       <c r="L4">
-        <v>0.03461538461538461</v>
+        <v>-0.6650246305418719</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,7 +880,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -889,79 +889,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>18.4</v>
+        <v>8.6</v>
       </c>
       <c r="V4">
-        <v>0.448780487804878</v>
+        <v>0.3739130434782609</v>
       </c>
       <c r="W4">
-        <v>0.01257189811010682</v>
+        <v>-0.2106084243369735</v>
       </c>
       <c r="X4">
-        <v>0.07035642764490212</v>
+        <v>0.1310327862671925</v>
       </c>
       <c r="Y4">
-        <v>-0.0577845295347953</v>
+        <v>-0.341641210604166</v>
       </c>
       <c r="Z4">
-        <v>0.5322095123419627</v>
+        <v>0.381328073635766</v>
       </c>
       <c r="AA4">
-        <v>0.03226971703792896</v>
+        <v>-0.1089508781816474</v>
       </c>
       <c r="AB4">
-        <v>0.06665285797185083</v>
+        <v>0.1002790675491828</v>
       </c>
       <c r="AC4">
-        <v>-0.03438314093392187</v>
+        <v>-0.2092299457308302</v>
       </c>
       <c r="AD4">
-        <v>3.69</v>
+        <v>13.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.69</v>
+        <v>13.3</v>
       </c>
       <c r="AG4">
-        <v>-14.71</v>
+        <v>4.700000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.08256880733944955</v>
+        <v>0.3663911845730028</v>
       </c>
       <c r="AI4">
-        <v>0.02838679898453727</v>
+        <v>0.1464757709251101</v>
       </c>
       <c r="AJ4">
-        <v>-0.5595283377710156</v>
+        <v>0.1696750902527076</v>
       </c>
       <c r="AK4">
-        <v>-0.1318218478358276</v>
+        <v>0.05717761557177617</v>
       </c>
       <c r="AL4">
-        <v>0.254</v>
+        <v>0.963</v>
       </c>
       <c r="AM4">
-        <v>0.254</v>
+        <v>0.963</v>
       </c>
       <c r="AN4">
-        <v>0.582018927444795</v>
+        <v>-1.254716981132076</v>
       </c>
       <c r="AO4">
-        <v>21.10236220472441</v>
+        <v>-12.04569055036345</v>
       </c>
       <c r="AP4">
-        <v>-2.320189274447949</v>
+        <v>-0.4433962264150945</v>
       </c>
       <c r="AQ4">
-        <v>21.10236220472441</v>
+        <v>-12.04569055036345</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00233</v>
+        <v>0.0154</v>
       </c>
       <c r="E2">
-        <v>-0.0211</v>
+        <v>0.205</v>
       </c>
       <c r="G2">
-        <v>0.06556245686680469</v>
+        <v>0.01386567626121944</v>
       </c>
       <c r="H2">
-        <v>0.06556245686680469</v>
+        <v>0.01386567626121944</v>
       </c>
       <c r="I2">
-        <v>-0.01573498964803312</v>
+        <v>0.02760755184153514</v>
       </c>
       <c r="J2">
-        <v>-0.01401961782574755</v>
+        <v>0.02445455821591719</v>
       </c>
       <c r="K2">
-        <v>-17.43</v>
+        <v>12.31</v>
       </c>
       <c r="L2">
-        <v>-0.06014492753623188</v>
+        <v>0.03809965954812752</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="N2">
-        <v>0.00900163666121113</v>
+        <v>0.01800699300699301</v>
       </c>
       <c r="O2">
-        <v>-0.06310958118187035</v>
+        <v>0.1673436230706743</v>
       </c>
       <c r="P2">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
-        <v>0.00900163666121113</v>
+        <v>0.01800699300699301</v>
       </c>
       <c r="R2">
-        <v>-0.06310958118187035</v>
+        <v>0.1673436230706743</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>69.09999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="V2">
-        <v>0.5654664484451718</v>
+        <v>0.5627622377622377</v>
       </c>
       <c r="W2">
-        <v>-0.08399967076154106</v>
+        <v>0.02380110311144794</v>
       </c>
       <c r="X2">
-        <v>0.1170504694703369</v>
+        <v>0.1070818127586321</v>
       </c>
       <c r="Y2">
-        <v>-0.2010501402318779</v>
+        <v>-0.08328070964718419</v>
       </c>
       <c r="Z2">
-        <v>1.037200346449253</v>
+        <v>1.444306366391603</v>
       </c>
       <c r="AA2">
-        <v>-0.03855900416597328</v>
+        <v>0.00183181265637665</v>
       </c>
       <c r="AB2">
-        <v>0.1015623355909855</v>
+        <v>0.08771469906768972</v>
       </c>
       <c r="AC2">
-        <v>-0.1401213397569588</v>
+        <v>-0.08588288641131306</v>
       </c>
       <c r="AD2">
-        <v>13.696</v>
+        <v>23.452</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.696</v>
+        <v>23.452</v>
       </c>
       <c r="AG2">
-        <v>-55.404</v>
+        <v>-40.928</v>
       </c>
       <c r="AH2">
-        <v>0.1007829516689233</v>
+        <v>0.1701244813278008</v>
       </c>
       <c r="AI2">
-        <v>0.04655399801492882</v>
+        <v>0.06686205638171699</v>
       </c>
       <c r="AJ2">
-        <v>-0.8294508653212765</v>
+        <v>-0.5570557491289198</v>
       </c>
       <c r="AK2">
-        <v>-0.2461349824075061</v>
+        <v>-0.1429190004609389</v>
       </c>
       <c r="AL2">
-        <v>0.966</v>
+        <v>1.447</v>
       </c>
       <c r="AM2">
-        <v>0.966</v>
+        <v>1.447</v>
       </c>
       <c r="AN2">
-        <v>-6.253881278538815</v>
+        <v>2.073563218390804</v>
       </c>
       <c r="AO2">
-        <v>-4.720496894409938</v>
+        <v>6.164478230822393</v>
       </c>
       <c r="AP2">
-        <v>25.2986301369863</v>
+        <v>-3.618744473916887</v>
       </c>
       <c r="AQ2">
-        <v>-4.720496894409938</v>
+        <v>6.164478230822393</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00233</v>
+        <v>0.0154</v>
       </c>
       <c r="E3">
-        <v>-0.0211</v>
+        <v>0.205</v>
       </c>
       <c r="G3">
-        <v>0.119983948635634</v>
+        <v>0.02239827151602449</v>
       </c>
       <c r="H3">
-        <v>0.119983948635634</v>
+        <v>0.02239827151602449</v>
       </c>
       <c r="I3">
-        <v>0.02825040128410915</v>
+        <v>0.05509542671948146</v>
       </c>
       <c r="J3">
-        <v>0.0220908875615083</v>
+        <v>0.04251078826661629</v>
       </c>
       <c r="K3">
-        <v>9.57</v>
+        <v>14.1</v>
       </c>
       <c r="L3">
-        <v>0.03840288924558588</v>
+        <v>0.05077421678069859</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="N3">
-        <v>0.01108870967741936</v>
+        <v>0.0225382932166302</v>
       </c>
       <c r="O3">
-        <v>0.1149425287356322</v>
+        <v>0.1460992907801419</v>
       </c>
       <c r="P3">
-        <v>1.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>0.01108870967741936</v>
+        <v>0.0225382932166302</v>
       </c>
       <c r="R3">
-        <v>0.1149425287356322</v>
+        <v>0.1460992907801419</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="V3">
-        <v>0.6098790322580645</v>
+        <v>0.6728665207877461</v>
       </c>
       <c r="W3">
-        <v>0.04260908281389136</v>
+        <v>0.06945812807881774</v>
       </c>
       <c r="X3">
-        <v>0.1030681526734813</v>
+        <v>0.08848354025491457</v>
       </c>
       <c r="Y3">
-        <v>-0.06045906985958989</v>
+        <v>-0.01902541217609684</v>
       </c>
       <c r="Z3">
-        <v>1.440995512790859</v>
+        <v>1.94337140297839</v>
       </c>
       <c r="AA3">
-        <v>0.03183286984970086</v>
+        <v>0.08261425023541139</v>
       </c>
       <c r="AB3">
-        <v>0.1028456036327882</v>
+        <v>0.0882174524032993</v>
       </c>
       <c r="AC3">
-        <v>-0.07101273378308735</v>
+        <v>-0.005603202167887913</v>
       </c>
       <c r="AD3">
-        <v>0.396</v>
+        <v>0.552</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.396</v>
+        <v>0.552</v>
       </c>
       <c r="AG3">
-        <v>-60.104</v>
+        <v>-60.948</v>
       </c>
       <c r="AH3">
-        <v>0.003976063295714687</v>
+        <v>0.006003132068905515</v>
       </c>
       <c r="AI3">
-        <v>0.001946940942791402</v>
+        <v>0.002142424665828326</v>
       </c>
       <c r="AJ3">
-        <v>-1.537343973808062</v>
+        <v>-2.001444896886904</v>
       </c>
       <c r="AK3">
-        <v>-0.420613593102676</v>
+        <v>-0.3107182185244096</v>
       </c>
       <c r="AL3">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AN3">
-        <v>0.04708680142687277</v>
+        <v>0.03325301204819277</v>
       </c>
       <c r="AO3">
-        <v>2346.666666666667</v>
+        <v>2185.714285714286</v>
       </c>
       <c r="AP3">
-        <v>-7.146730083234245</v>
+        <v>-3.671566265060241</v>
       </c>
       <c r="AQ3">
-        <v>2346.666666666667</v>
+        <v>2185.714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.2684729064039409</v>
+        <v>-0.03832599118942731</v>
       </c>
       <c r="H4">
-        <v>-0.2684729064039409</v>
+        <v>-0.03832599118942731</v>
       </c>
       <c r="I4">
-        <v>-0.2857142857142857</v>
+        <v>-0.1405286343612335</v>
       </c>
       <c r="J4">
-        <v>-0.2857142857142857</v>
+        <v>-0.1405286343612335</v>
       </c>
       <c r="K4">
-        <v>-27</v>
+        <v>-1.79</v>
       </c>
       <c r="L4">
-        <v>-0.6650246305418719</v>
+        <v>-0.0394273127753304</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,73 +895,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8.6</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
-        <v>0.3739130434782609</v>
+        <v>0.1252173913043478</v>
       </c>
       <c r="W4">
-        <v>-0.2106084243369735</v>
+        <v>-0.02185592185592185</v>
       </c>
       <c r="X4">
-        <v>0.1310327862671925</v>
+        <v>0.1256800852623497</v>
       </c>
       <c r="Y4">
-        <v>-0.341641210604166</v>
+        <v>-0.1475360071182716</v>
       </c>
       <c r="Z4">
-        <v>0.381328073635766</v>
+        <v>0.5618116569731468</v>
       </c>
       <c r="AA4">
-        <v>-0.1089508781816474</v>
+        <v>-0.07895062492265809</v>
       </c>
       <c r="AB4">
-        <v>0.1002790675491828</v>
+        <v>0.08721194573208015</v>
       </c>
       <c r="AC4">
-        <v>-0.2092299457308302</v>
+        <v>-0.1661625706547382</v>
       </c>
       <c r="AD4">
-        <v>13.3</v>
+        <v>22.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>13.3</v>
+        <v>22.9</v>
       </c>
       <c r="AG4">
-        <v>4.700000000000001</v>
+        <v>20.02</v>
       </c>
       <c r="AH4">
-        <v>0.3663911845730028</v>
+        <v>0.4989106753812636</v>
       </c>
       <c r="AI4">
-        <v>0.1464757709251101</v>
+        <v>0.2459720730397422</v>
       </c>
       <c r="AJ4">
-        <v>0.1696750902527076</v>
+        <v>0.4653649465364947</v>
       </c>
       <c r="AK4">
-        <v>0.05717761557177617</v>
+        <v>0.2219020172910663</v>
       </c>
       <c r="AL4">
-        <v>0.963</v>
+        <v>1.44</v>
       </c>
       <c r="AM4">
-        <v>0.963</v>
+        <v>1.44</v>
       </c>
       <c r="AN4">
-        <v>-1.254716981132076</v>
+        <v>-4.328922495274102</v>
       </c>
       <c r="AO4">
-        <v>-12.04569055036345</v>
+        <v>-4.430555555555555</v>
       </c>
       <c r="AP4">
-        <v>-0.4433962264150945</v>
+        <v>-3.784499054820416</v>
       </c>
       <c r="AQ4">
-        <v>-12.04569055036345</v>
+        <v>-4.430555555555555</v>
       </c>
     </row>
   </sheetData>
